--- a/invalidCodes/invalidCodes_Parker.xlsx.xlsx
+++ b/invalidCodes/invalidCodes_Parker.xlsx.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,21 +488,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ELE</t>
+          <t>MOB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FDC20HP-00000000</t>
+          <t>08650664</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FD20HP ROLLER CASSETTE</t>
+          <t>SP-4-4-HP-1500</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17512.14</v>
+        <v>23210.91</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
@@ -522,26 +522,30 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Descto PL -56.%  Válvulas Mobile. Net OC&gt;=$200,000</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ELE</t>
+          <t>MOB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PSD1SW1300C2202000</t>
+          <t>CFQ-A-12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PSD Stand-Alone Drive 230VAC</t>
+          <t>VALVULA HCA DE CONTROL FLUJO</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>63070.31</v>
+        <v>8286.040000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -549,10 +553,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
@@ -561,26 +565,30 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Descto PL -56.%  Válvulas Mobile. Net OC&gt;=$200,000</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HFD</t>
+          <t>MOB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EAC10P020</t>
+          <t>CFQ-A-50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FILTER ELEMENT</t>
+          <t>VALVULA REGULADORA FLUJO</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>650.01</v>
+        <v>8588.51</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -588,10 +596,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
@@ -600,26 +608,30 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Descto PL -56.%  Válvulas Mobile. Net OC&gt;=$200,000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HID</t>
+          <t>MOB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9MV1200S</t>
+          <t>S-50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>METERING VALVE</t>
+          <t>SELECTOR VALVE 1/2 NPT</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8090.94</v>
+        <v>3996.63</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -627,10 +639,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
@@ -639,128 +651,11 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>HID</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AD03SPS6P</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>D03 SUBPLATE</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>4860</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G6" t="n">
-        <v>75</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NEU</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0865130151</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>PROMO 0150 MAGNETIC RING 2MA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>755.22</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Descto PL -55.%  Kits sellos Cilindros . Net OC&gt;=$100,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NEU</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>KV38C43</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>HP DIAPHRAGM AIR RETURN</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>15861.83</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>76</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Descto PL -56.%  Válvulas Mobile. Net OC&gt;=$200,000</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/invalidCodes/invalidCodes_Parker.xlsx.xlsx
+++ b/invalidCodes/invalidCodes_Parker.xlsx.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,235 +413,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Linea</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Descripcion de Producto</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Precio de Lista MXP</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>UM</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Existencia Disponible</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LeadTime Dias Habiles</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Cantidad Multiplo de Compra</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Cantidad Minima de Compra</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Promoción</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MOB</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>08650664</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SP-4-4-HP-1500</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>23210.91</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>55</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Descto PL -56.%  Válvulas Mobile. Net OC&gt;=$200,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MOB</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CFQ-A-12</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VALVULA HCA DE CONTROL FLUJO</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>8286.040000000001</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>13</v>
-      </c>
-      <c r="G3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Descto PL -56.%  Válvulas Mobile. Net OC&gt;=$200,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MOB</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CFQ-A-50</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VALVULA REGULADORA FLUJO</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>8588.51</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G4" t="n">
-        <v>40</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Descto PL -56.%  Válvulas Mobile. Net OC&gt;=$200,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MOB</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>S-50</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SELECTOR VALVE 1/2 NPT</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3996.63</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>42</v>
-      </c>
-      <c r="G5" t="n">
-        <v>40</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Descto PL -56.%  Válvulas Mobile. Net OC&gt;=$200,000</t>
         </is>
       </c>
     </row>
